--- a/data/trans_orig/P16A13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>35534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61845</t>
+          <t>62251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>57329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>91616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100211</t>
+          <t>100670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140693</t>
+          <t>144423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969878</t>
+          <t>969472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>996425</t>
+          <t>996189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1224819</t>
+          <t>1223497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1255099</t>
+          <t>1257784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2206142</t>
+          <t>2202412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2246624</t>
+          <t>2246165</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36552</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>56158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84269</t>
+          <t>83380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1655842</t>
+          <t>1655487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1677587</t>
+          <t>1676731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1531332</t>
+          <t>1531515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1556673</t>
+          <t>1556607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3195798</t>
+          <t>3196687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3227711</t>
+          <t>3229453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33309</t>
+          <t>33215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524953</t>
+          <t>524891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541598</t>
+          <t>542085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462497</t>
+          <t>462731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473533</t>
+          <t>473500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>994511</t>
+          <t>994605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1013539</t>
+          <t>1012758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>142806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178837</t>
+          <t>181139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234861</t>
+          <t>237608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3166911</t>
+          <t>3168704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3204908</t>
+          <t>3204949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3236809</t>
+          <t>3236391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3277276</t>
+          <t>3277638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6419861</t>
+          <t>6417114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6475885</t>
+          <t>6473583</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50841</t>
+          <t>51902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>86587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89793</t>
+          <t>90908</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130703</t>
+          <t>130133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151528</t>
+          <t>153407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201580</t>
+          <t>204693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>882705</t>
+          <t>881887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>917633</t>
+          <t>916572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1202824</t>
+          <t>1203394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1243734</t>
+          <t>1242619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2100421</t>
+          <t>2097308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2150473</t>
+          <t>2148594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>41275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>72720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>40912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74452</t>
+          <t>74819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89382</t>
+          <t>90636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134188</t>
+          <t>137830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1886664</t>
+          <t>1887302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1918056</t>
+          <t>1918747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1677397</t>
+          <t>1677030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1709474</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3577683</t>
+          <t>3574041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3622489</t>
+          <t>3621235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29888</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>35476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57463</t>
+          <t>57533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450444</t>
+          <t>451284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471121</t>
+          <t>470630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421554</t>
+          <t>422178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442311</t>
+          <t>442032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>880523</t>
+          <t>880453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>908874</t>
+          <t>907952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118920</t>
+          <t>117935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169603</t>
+          <t>167980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163920</t>
+          <t>165935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218766</t>
+          <t>221620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>291310</t>
+          <t>293730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>369802</t>
+          <t>370045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3239225</t>
+          <t>3240848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3289908</t>
+          <t>3290893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3324265</t>
+          <t>3321411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3379111</t>
+          <t>3377096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6582056</t>
+          <t>6581813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6660548</t>
+          <t>6658128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>24727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>47710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,82 +3954,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>73011</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57665</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>93549</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>108165</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>89042</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>132399</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73011</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>58041</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93534</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>108165</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>87536</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>131181</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>707696</t>
+          <t>706637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>729234</t>
+          <t>729620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,82 +4067,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>921649</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>901111</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>936995</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1640842</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1616608</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1659965</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>93,82%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>921649</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>901126</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>936619</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,6%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1555</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1640842</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1617826</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1661471</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>35230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66712</t>
+          <t>66171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39742</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71398</t>
+          <t>68616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82983</t>
+          <t>81632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125031</t>
+          <t>123328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2009673</t>
+          <t>2010214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2040448</t>
+          <t>2041155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1916902</t>
+          <t>1919684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1948558</t>
+          <t>1948282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3939654</t>
+          <t>3941357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3981702</t>
+          <t>3983053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26418</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>28768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>21516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>47589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520468</t>
+          <t>520831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539069</t>
+          <t>538763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519966</t>
+          <t>520372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539267</t>
+          <t>538392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1048598</t>
+          <t>1048438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073206</t>
+          <t>1074511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80501</t>
+          <t>80671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120900</t>
+          <t>118891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117570</t>
+          <t>120814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169868</t>
+          <t>171423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211615</t>
+          <t>213629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279675</t>
+          <t>275331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3256718</t>
+          <t>3258727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3297117</t>
+          <t>3296947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3362232</t>
+          <t>3360677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3414530</t>
+          <t>3411286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6630043</t>
+          <t>6634387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6698103</t>
+          <t>6696089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80364</t>
+          <t>80681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125185</t>
+          <t>123010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155409</t>
+          <t>153331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>185966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223792</t>
+          <t>225323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433578</t>
+          <t>433261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459752</t>
+          <t>460019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>596653</t>
+          <t>598731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>626877</t>
+          <t>629052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1042212</t>
+          <t>1040681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1080168</t>
+          <t>1080038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>72493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130967</t>
+          <t>128812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>83963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139672</t>
+          <t>140056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>178467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260210</t>
+          <t>256143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2159360</t>
+          <t>2161515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2218739</t>
+          <t>2217834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2097473</t>
+          <t>2097089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2153831</t>
+          <t>2153182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4267262</t>
+          <t>4271329</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4348546</t>
+          <t>4349005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48238</t>
+          <t>48219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55936</t>
+          <t>54955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82373</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598385</t>
+          <t>598404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619538</t>
+          <t>619215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619859</t>
+          <t>619696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637018</t>
+          <t>637139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1224713</t>
+          <t>1224429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1251150</t>
+          <t>1252131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165461</t>
+          <t>158642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241383</t>
+          <t>242572</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>240468</t>
+          <t>228482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316408</t>
+          <t>318775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>433925</t>
+          <t>426520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>543076</t>
+          <t>546982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3209509</t>
+          <t>3208320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3285431</t>
+          <t>3292250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3333262</t>
+          <t>3330895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3409202</t>
+          <t>3421188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6557486</t>
+          <t>6553580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6666637</t>
+          <t>6674042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35534</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62251</t>
+          <t>61573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57329</t>
+          <t>56822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91616</t>
+          <t>90311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100670</t>
+          <t>99272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144423</t>
+          <t>141261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969472</t>
+          <t>970150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>996189</t>
+          <t>997191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1223497</t>
+          <t>1224802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1257784</t>
+          <t>1258291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2202412</t>
+          <t>2205574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2246165</t>
+          <t>2247563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31066</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56158</t>
+          <t>56241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83380</t>
+          <t>81923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1655487</t>
+          <t>1657210</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1676731</t>
+          <t>1677231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1531515</t>
+          <t>1531432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1556607</t>
+          <t>1558040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3196687</t>
+          <t>3198144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3229453</t>
+          <t>3227723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>25007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>34516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524891</t>
+          <t>526401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542085</t>
+          <t>542945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462731</t>
+          <t>462714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473500</t>
+          <t>473493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>994605</t>
+          <t>993304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1012758</t>
+          <t>1012804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>105971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>102113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142806</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>182237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237608</t>
+          <t>239500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3168704</t>
+          <t>3169554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3204949</t>
+          <t>3205352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3236391</t>
+          <t>3236253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3277638</t>
+          <t>3277084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6417114</t>
+          <t>6415222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6473583</t>
+          <t>6472485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>51610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86587</t>
+          <t>85786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90908</t>
+          <t>90397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130133</t>
+          <t>129929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153407</t>
+          <t>152734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204693</t>
+          <t>206904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>881887</t>
+          <t>882688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>916572</t>
+          <t>916864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1203394</t>
+          <t>1203598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1242619</t>
+          <t>1243130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2097308</t>
+          <t>2095097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2148594</t>
+          <t>2149267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41275</t>
+          <t>42152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72720</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90636</t>
+          <t>92051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137830</t>
+          <t>138259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1887302</t>
+          <t>1887062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1918747</t>
+          <t>1917870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1677030</t>
+          <t>1678179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3574041</t>
+          <t>3573612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3621235</t>
+          <t>3619820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>30396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35476</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451284</t>
+          <t>449936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470630</t>
+          <t>470830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>422178</t>
+          <t>421554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442032</t>
+          <t>441992</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>880453</t>
+          <t>878762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>907952</t>
+          <t>908706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117935</t>
+          <t>117823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167980</t>
+          <t>165599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165935</t>
+          <t>163640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221620</t>
+          <t>218267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293730</t>
+          <t>294564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370045</t>
+          <t>370769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3240848</t>
+          <t>3243229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3290893</t>
+          <t>3291005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3321411</t>
+          <t>3324764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3377096</t>
+          <t>3379391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6581813</t>
+          <t>6581089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6658128</t>
+          <t>6657294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>47156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57665</t>
+          <t>57595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>92832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89042</t>
+          <t>88641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132399</t>
+          <t>128668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>706637</t>
+          <t>707191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>729620</t>
+          <t>729441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>901111</t>
+          <t>901828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>936995</t>
+          <t>937065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1616608</t>
+          <t>1620339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1659965</t>
+          <t>1660366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66171</t>
+          <t>65320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>39641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>70714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81632</t>
+          <t>80853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123328</t>
+          <t>124578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2010214</t>
+          <t>2011065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2041155</t>
+          <t>2040643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1919684</t>
+          <t>1917586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1948282</t>
+          <t>1948659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3941357</t>
+          <t>3940107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3983053</t>
+          <t>3983832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,47 +4675,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>32440</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>21508</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>46271</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>32440</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>21516</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>47589</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520831</t>
+          <t>521453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538763</t>
+          <t>539035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520372</t>
+          <t>520342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538392</t>
+          <t>539258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1048438</t>
+          <t>1049756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074511</t>
+          <t>1074519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80671</t>
+          <t>80862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118891</t>
+          <t>121689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120814</t>
+          <t>121789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171423</t>
+          <t>172967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213629</t>
+          <t>214066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275331</t>
+          <t>276682</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3258727</t>
+          <t>3255929</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3296947</t>
+          <t>3296756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3360677</t>
+          <t>3359133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3411286</t>
+          <t>3410311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6634387</t>
+          <t>6633036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6696089</t>
+          <t>6695652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66402</t>
+          <t>70451</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53923</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>138401</t>
+          <t>147657</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123010</t>
+          <t>132474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153331</t>
+          <t>163596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>204803</t>
+          <t>218108</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185966</t>
+          <t>197983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225323</t>
+          <t>240086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>447540</t>
+          <t>507091</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433261</t>
+          <t>492221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460019</t>
+          <t>519443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>613661</t>
+          <t>672459</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598731</t>
+          <t>656520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>629052</t>
+          <t>687642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1061201</t>
+          <t>1179550</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1040681</t>
+          <t>1157572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1080038</t>
+          <t>1199675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>104212</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72493</t>
+          <t>91775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>127927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116987</t>
+          <t>128761</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83963</t>
+          <t>111794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140056</t>
+          <t>146733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>221199</t>
+          <t>235896</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178467</t>
+          <t>211461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256143</t>
+          <t>264148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2186115</t>
+          <t>2123431</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2161515</t>
+          <t>2102639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2217834</t>
+          <t>2138791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2120158</t>
+          <t>2041946</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2097089</t>
+          <t>2023974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2153182</t>
+          <t>2058913</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4306273</t>
+          <t>4165378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4271329</t>
+          <t>4137126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4349005</t>
+          <t>4189813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>56264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>35633</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>46306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67412</t>
+          <t>77811</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54955</t>
+          <t>64203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>609744</t>
+          <t>669409</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598404</t>
+          <t>655323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619215</t>
+          <t>679509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>629930</t>
+          <t>699244</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619696</t>
+          <t>688571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>637139</t>
+          <t>707358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1239674</t>
+          <t>1368653</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1224429</t>
+          <t>1353068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252131</t>
+          <t>1382261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>207493</t>
+          <t>219764</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>194517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242572</t>
+          <t>248788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>285921</t>
+          <t>312051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228482</t>
+          <t>285878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>318775</t>
+          <t>338123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>493414</t>
+          <t>531815</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>426520</t>
+          <t>499886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>546982</t>
+          <t>571073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3243399</t>
+          <t>3299931</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3208320</t>
+          <t>3270907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3292250</t>
+          <t>3325178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3363749</t>
+          <t>3413650</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3330895</t>
+          <t>3387578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3421188</t>
+          <t>3439823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6607148</t>
+          <t>6713581</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6553580</t>
+          <t>6674323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6674042</t>
+          <t>6745510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
